--- a/RevGame_Client/配置表/战斗弹幕配置.xlsx
+++ b/RevGame_Client/配置表/战斗弹幕配置.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleText" sheetId="1" r:id="Ra0be674ea1944ade"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleTuning" sheetId="2" r:id="Rb8eba556a42443a7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="3" r:id="Ra7aeff4f830b4530"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleText" sheetId="1" r:id="R022dbe22a85b4889"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleTuning" sheetId="2" r:id="R4cfbcbf1171b4620"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="3" r:id="R9bd75f3bf0b9412b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -72,7 +72,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="18">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -113,6 +113,9 @@
     </x:xf>
     <x:xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1063,14 +1066,557 @@
         <x:v>1.3</x:v>
       </x:c>
     </x:row>
-    <x:row r="31">
-      <x:c r="A31" t="str"/>
-      <x:c r="B31" t="str"/>
-      <x:c r="C31" t="str"/>
-      <x:c r="D31" t="str"/>
-      <x:c r="E31" t="str"/>
-      <x:c r="F31" t="str"/>
-      <x:c r="G31" t="str"/>
+    <x:row r="31" ht="32" customHeight="1">
+      <x:c r="A31" s="17" t="str">
+        <x:v>Damage_Incoming</x:v>
+      </x:c>
+      <x:c r="B31" s="17" t="str">
+        <x:v>受击 -{damage}</x:v>
+      </x:c>
+      <x:c r="C31" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D31" s="17" t="str">
+        <x:v>#FF818A</x:v>
+      </x:c>
+      <x:c r="E31" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F31" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G31" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="32" customHeight="1">
+      <x:c r="A32" s="17" t="str">
+        <x:v>Damage_Critical</x:v>
+      </x:c>
+      <x:c r="B32" s="17" t="str">
+        <x:v>暴击！ -{damage}</x:v>
+      </x:c>
+      <x:c r="C32" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D32" s="17" t="str">
+        <x:v>#FF921F</x:v>
+      </x:c>
+      <x:c r="E32" s="17" t="n">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="F32" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G32" s="17" t="n">
+        <x:v>1.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="32" customHeight="1">
+      <x:c r="A33" s="17" t="str">
+        <x:v>Damage_RegionPulse</x:v>
+      </x:c>
+      <x:c r="B33" s="17" t="str">
+        <x:v>区域波动 -{damage}</x:v>
+      </x:c>
+      <x:c r="C33" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D33" s="17" t="str">
+        <x:v>#53E6DF</x:v>
+      </x:c>
+      <x:c r="E33" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F33" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G33" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="32" customHeight="1">
+      <x:c r="A34" s="17" t="str">
+        <x:v>Damage_EnergyBomb</x:v>
+      </x:c>
+      <x:c r="B34" s="17" t="str">
+        <x:v>能量巨大 -{damage}</x:v>
+      </x:c>
+      <x:c r="C34" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D34" s="17" t="str">
+        <x:v>#ED83FF</x:v>
+      </x:c>
+      <x:c r="E34" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F34" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G34" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="32" customHeight="1">
+      <x:c r="A35" s="17" t="str">
+        <x:v>Damage_Artillery</x:v>
+      </x:c>
+      <x:c r="B35" s="17" t="str">
+        <x:v>炮火支援 -{damage}</x:v>
+      </x:c>
+      <x:c r="C35" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D35" s="17" t="str">
+        <x:v>#FFD09D</x:v>
+      </x:c>
+      <x:c r="E35" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F35" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G35" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="32" customHeight="1">
+      <x:c r="A36" s="17" t="str">
+        <x:v>Damage_Execution</x:v>
+      </x:c>
+      <x:c r="B36" s="17" t="str">
+        <x:v>断链 -{damage}</x:v>
+      </x:c>
+      <x:c r="C36" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D36" s="17" t="str">
+        <x:v>#BBA6FF</x:v>
+      </x:c>
+      <x:c r="E36" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F36" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G36" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="32" customHeight="1">
+      <x:c r="A37" s="17" t="str">
+        <x:v>Damage_BossCleave</x:v>
+      </x:c>
+      <x:c r="B37" s="17" t="str">
+        <x:v>震地 -{damage}</x:v>
+      </x:c>
+      <x:c r="C37" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D37" s="17" t="str">
+        <x:v>#D9AC76</x:v>
+      </x:c>
+      <x:c r="E37" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F37" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G37" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="32" customHeight="1">
+      <x:c r="A38" s="17" t="str">
+        <x:v>Damage_BossSnipe</x:v>
+      </x:c>
+      <x:c r="B38" s="17" t="str">
+        <x:v>狙击 -{damage}</x:v>
+      </x:c>
+      <x:c r="C38" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D38" s="17" t="str">
+        <x:v>#FF577C</x:v>
+      </x:c>
+      <x:c r="E38" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F38" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G38" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="32" customHeight="1">
+      <x:c r="A39" s="17" t="str">
+        <x:v>Damage_BossBombard</x:v>
+      </x:c>
+      <x:c r="B39" s="17" t="str">
+        <x:v>轰炸 -{damage}</x:v>
+      </x:c>
+      <x:c r="C39" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D39" s="17" t="str">
+        <x:v>#FFAA57</x:v>
+      </x:c>
+      <x:c r="E39" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F39" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G39" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="32" customHeight="1">
+      <x:c r="A40" s="17" t="str">
+        <x:v>Damage_BossBulletRing</x:v>
+      </x:c>
+      <x:c r="B40" s="17" t="str">
+        <x:v>弹幕 -{damage}</x:v>
+      </x:c>
+      <x:c r="C40" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D40" s="17" t="str">
+        <x:v>#EF7CCA</x:v>
+      </x:c>
+      <x:c r="E40" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F40" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G40" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="32" customHeight="1">
+      <x:c r="A41" s="17" t="str">
+        <x:v>Damage_BossBlinkBlast</x:v>
+      </x:c>
+      <x:c r="B41" s="17" t="str">
+        <x:v>瞬爆 -{damage}</x:v>
+      </x:c>
+      <x:c r="C41" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D41" s="17" t="str">
+        <x:v>#BC85FF</x:v>
+      </x:c>
+      <x:c r="E41" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F41" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G41" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="32" customHeight="1">
+      <x:c r="A42" s="17" t="str">
+        <x:v>Damage_BossLaserSpin</x:v>
+      </x:c>
+      <x:c r="B42" s="17" t="str">
+        <x:v>天光 -{damage}</x:v>
+      </x:c>
+      <x:c r="C42" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D42" s="17" t="str">
+        <x:v>#FFF09E</x:v>
+      </x:c>
+      <x:c r="E42" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F42" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G42" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="32" customHeight="1">
+      <x:c r="A43" s="17" t="str">
+        <x:v>Damage_BossSoulDrain</x:v>
+      </x:c>
+      <x:c r="B43" s="17" t="str">
+        <x:v>汲魂 -{damage}</x:v>
+      </x:c>
+      <x:c r="C43" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D43" s="17" t="str">
+        <x:v>#B59AFF</x:v>
+      </x:c>
+      <x:c r="E43" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F43" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G43" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="32" customHeight="1">
+      <x:c r="A44" s="17" t="str">
+        <x:v>Damage_BossSummon</x:v>
+      </x:c>
+      <x:c r="B44" s="17" t="str">
+        <x:v>影卫 -{damage}</x:v>
+      </x:c>
+      <x:c r="C44" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D44" s="17" t="str">
+        <x:v>#B7A0F2</x:v>
+      </x:c>
+      <x:c r="E44" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F44" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G44" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="32" customHeight="1">
+      <x:c r="A45" s="17" t="str">
+        <x:v>Damage_BossEnrage</x:v>
+      </x:c>
+      <x:c r="B45" s="17" t="str">
+        <x:v>狂怒 -{damage}</x:v>
+      </x:c>
+      <x:c r="C45" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D45" s="17" t="str">
+        <x:v>#FF5252</x:v>
+      </x:c>
+      <x:c r="E45" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F45" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G45" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="32" customHeight="1">
+      <x:c r="A46" s="17" t="str">
+        <x:v>Damage_BossMeteorShower</x:v>
+      </x:c>
+      <x:c r="B46" s="17" t="str">
+        <x:v>陨星 -{damage}</x:v>
+      </x:c>
+      <x:c r="C46" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D46" s="17" t="str">
+        <x:v>#FF793E</x:v>
+      </x:c>
+      <x:c r="E46" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F46" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G46" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="32" customHeight="1">
+      <x:c r="A47" s="17" t="str">
+        <x:v>Damage_BossCrossLaser</x:v>
+      </x:c>
+      <x:c r="B47" s="17" t="str">
+        <x:v>天罚 -{damage}</x:v>
+      </x:c>
+      <x:c r="C47" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D47" s="17" t="str">
+        <x:v>#FFF8B2</x:v>
+      </x:c>
+      <x:c r="E47" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F47" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G47" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="32" customHeight="1">
+      <x:c r="A48" s="17" t="str">
+        <x:v>Damage_BossFrostNova</x:v>
+      </x:c>
+      <x:c r="B48" s="17" t="str">
+        <x:v>冰霜 -{damage}</x:v>
+      </x:c>
+      <x:c r="C48" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D48" s="17" t="str">
+        <x:v>#73DFFF</x:v>
+      </x:c>
+      <x:c r="E48" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F48" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G48" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="32" customHeight="1">
+      <x:c r="A49" s="17" t="str">
+        <x:v>Damage_BossChainLightning</x:v>
+      </x:c>
+      <x:c r="B49" s="17" t="str">
+        <x:v>雷暴 -{damage}</x:v>
+      </x:c>
+      <x:c r="C49" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D49" s="17" t="str">
+        <x:v>#A7A1FF</x:v>
+      </x:c>
+      <x:c r="E49" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F49" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G49" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="32" customHeight="1">
+      <x:c r="A50" s="17" t="str">
+        <x:v>Damage_BossPoisonMarsh</x:v>
+      </x:c>
+      <x:c r="B50" s="17" t="str">
+        <x:v>毒沼 -{damage}</x:v>
+      </x:c>
+      <x:c r="C50" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D50" s="17" t="str">
+        <x:v>#A3ED56</x:v>
+      </x:c>
+      <x:c r="E50" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F50" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G50" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="32" customHeight="1">
+      <x:c r="A51" s="17" t="str">
+        <x:v>Damage_BossFlameWall</x:v>
+      </x:c>
+      <x:c r="B51" s="17" t="str">
+        <x:v>烈焰 -{damage}</x:v>
+      </x:c>
+      <x:c r="C51" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D51" s="17" t="str">
+        <x:v>#FFAC42</x:v>
+      </x:c>
+      <x:c r="E51" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F51" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G51" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="32" customHeight="1">
+      <x:c r="A52" s="17" t="str">
+        <x:v>Damage_BossIceLance</x:v>
+      </x:c>
+      <x:c r="B52" s="17" t="str">
+        <x:v>冰枪 -{damage}</x:v>
+      </x:c>
+      <x:c r="C52" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D52" s="17" t="str">
+        <x:v>#9CF5FF</x:v>
+      </x:c>
+      <x:c r="E52" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F52" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G52" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="32" customHeight="1">
+      <x:c r="A53" s="17" t="str">
+        <x:v>Damage_BossGravityWell</x:v>
+      </x:c>
+      <x:c r="B53" s="17" t="str">
+        <x:v>引力 -{damage}</x:v>
+      </x:c>
+      <x:c r="C53" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D53" s="17" t="str">
+        <x:v>#C182F6</x:v>
+      </x:c>
+      <x:c r="E53" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F53" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G53" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="32" customHeight="1">
+      <x:c r="A54" s="17" t="str">
+        <x:v>Damage_BossDoomSigil</x:v>
+      </x:c>
+      <x:c r="B54" s="17" t="str">
+        <x:v>烙印 -{damage}</x:v>
+      </x:c>
+      <x:c r="C54" s="17" t="str">
+        <x:v>真实扣血伤害；相同目标与同种来源才合并。</x:v>
+      </x:c>
+      <x:c r="D54" s="17" t="str">
+        <x:v>#F16AA9</x:v>
+      </x:c>
+      <x:c r="E54" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F54" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G54" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/RevGame_Client/配置表/战斗弹幕配置.xlsx
+++ b/RevGame_Client/配置表/战斗弹幕配置.xlsx
@@ -1051,7 +1051,7 @@
         <x:v>能量巨大</x:v>
       </x:c>
       <x:c r="C30" t="str">
-        <x:v>能量炸弹引爆！冲击全场敌军</x:v>
+        <x:v>每8秒对全场敌军扣除最大生命30%</x:v>
       </x:c>
       <x:c r="D30" t="str">
         <x:v>#FFE176</x:v>
@@ -1616,6 +1616,52 @@
       </x:c>
       <x:c r="G54" s="17" t="n">
         <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str" s="17">
+        <x:v>Event_眼位成型</x:v>
+      </x:c>
+      <x:c r="B55" t="str" s="17">
+        <x:v>眼位成型</x:v>
+      </x:c>
+      <x:c r="C55" t="str" s="17">
+        <x:v>眼位四邻：防御+{defense} · 每秒回复{regen}最大生命</x:v>
+      </x:c>
+      <x:c r="D55" t="str" s="17">
+        <x:v>#64F6DC</x:v>
+      </x:c>
+      <x:c r="E55" t="n" s="17">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F55" t="n" s="17">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G55" t="n" s="17">
+        <x:v>1.12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str" s="17">
+        <x:v>Event_眼位复苏</x:v>
+      </x:c>
+      <x:c r="B56" t="str" s="17">
+        <x:v>眼位复苏</x:v>
+      </x:c>
+      <x:c r="C56" t="str" s="17">
+        <x:v>驻眼棋原地复活 · 四邻友军回复{heal}最大生命</x:v>
+      </x:c>
+      <x:c r="D56" t="str" s="17">
+        <x:v>#FFF080</x:v>
+      </x:c>
+      <x:c r="E56" t="n" s="17">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="F56" t="n" s="17">
+        <x:v>2.8</x:v>
+      </x:c>
+      <x:c r="G56" t="n" s="17">
+        <x:v>1.12</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/RevGame_Client/配置表/战斗弹幕配置.xlsx
+++ b/RevGame_Client/配置表/战斗弹幕配置.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleText" sheetId="1" r:id="R022dbe22a85b4889"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleTuning" sheetId="2" r:id="R4cfbcbf1171b4620"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="3" r:id="R9bd75f3bf0b9412b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleText" sheetId="1" r:id="R2137ccf5ca7f4d33"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleTuning" sheetId="2" r:id="R6991917befa74458"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="3" r:id="R8557b1f5675749a2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1619,49 +1619,91 @@
       </x:c>
     </x:row>
     <x:row r="55">
-      <x:c r="A55" t="str" s="17">
+      <x:c r="A55" s="17" t="str">
         <x:v>Event_眼位成型</x:v>
       </x:c>
-      <x:c r="B55" t="str" s="17">
+      <x:c r="B55" s="17" t="str">
         <x:v>眼位成型</x:v>
       </x:c>
-      <x:c r="C55" t="str" s="17">
+      <x:c r="C55" s="17" t="str">
         <x:v>眼位四邻：防御+{defense} · 每秒回复{regen}最大生命</x:v>
       </x:c>
-      <x:c r="D55" t="str" s="17">
+      <x:c r="D55" s="17" t="str">
         <x:v>#64F6DC</x:v>
       </x:c>
-      <x:c r="E55" t="n" s="17">
+      <x:c r="E55" s="17" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F55" t="n" s="17">
+      <x:c r="F55" s="17" t="n">
         <x:v>2.8</x:v>
       </x:c>
-      <x:c r="G55" t="n" s="17">
+      <x:c r="G55" s="17" t="n">
         <x:v>1.12</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
-      <x:c r="A56" t="str" s="17">
+      <x:c r="A56" s="17" t="str">
         <x:v>Event_眼位复苏</x:v>
       </x:c>
-      <x:c r="B56" t="str" s="17">
+      <x:c r="B56" s="17" t="str">
         <x:v>眼位复苏</x:v>
       </x:c>
-      <x:c r="C56" t="str" s="17">
+      <x:c r="C56" s="17" t="str">
         <x:v>驻眼棋原地复活 · 四邻友军回复{heal}最大生命</x:v>
       </x:c>
-      <x:c r="D56" t="str" s="17">
+      <x:c r="D56" s="17" t="str">
         <x:v>#FFF080</x:v>
       </x:c>
-      <x:c r="E56" t="n" s="17">
+      <x:c r="E56" s="17" t="n">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="F56" t="n" s="17">
+      <x:c r="F56" s="17" t="n">
         <x:v>2.8</x:v>
       </x:c>
-      <x:c r="G56" t="n" s="17">
+      <x:c r="G56" s="17" t="n">
         <x:v>1.12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" s="2" t="str">
+        <x:v>Damage_Helper</x:v>
+      </x:c>
+      <x:c r="B57" s="2" t="str">
+        <x:v>-{damage}</x:v>
+      </x:c>
+      <x:c r="C57" s="2"/>
+      <x:c r="D57" s="2" t="str">
+        <x:v>#FFE52E</x:v>
+      </x:c>
+      <x:c r="E57" s="8" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F57" s="9" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="G57" s="9" t="n">
+        <x:v>1.35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" s="2" t="str">
+        <x:v>Damage_HelperBeam</x:v>
+      </x:c>
+      <x:c r="B58" s="2" t="str">
+        <x:v>-{damage}</x:v>
+      </x:c>
+      <x:c r="C58" s="2"/>
+      <x:c r="D58" s="2" t="str">
+        <x:v>#FFE52E</x:v>
+      </x:c>
+      <x:c r="E58" s="8" t="n">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="F58" s="9" t="n">
+        <x:v>1.6</x:v>
+      </x:c>
+      <x:c r="G58" s="9" t="n">
+        <x:v>1.35</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1720,7 +1762,7 @@
         </x:is>
       </x:c>
       <x:c r="B4" s="16" t="n">
-        <x:v>2</x:v>
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/RevGame_Client/配置表/战斗弹幕配置.xlsx
+++ b/RevGame_Client/配置表/战斗弹幕配置.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleText" sheetId="1" r:id="R2137ccf5ca7f4d33"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleTuning" sheetId="2" r:id="R6991917befa74458"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="3" r:id="R8557b1f5675749a2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleText" sheetId="1" r:id="R4cb15cb319b049e9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleTuning" sheetId="2" r:id="R1872830242e24b63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="3" r:id="R18be5be65f724ad3"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1706,6 +1706,282 @@
         <x:v>1.35</x:v>
       </x:c>
     </x:row>
+    <x:row r="59">
+      <x:c r="A59" s="17" t="str">
+        <x:v>Damage_BossStarStorm</x:v>
+      </x:c>
+      <x:c r="B59" s="17" t="str">
+        <x:v>星暴 -{damage}</x:v>
+      </x:c>
+      <x:c r="C59" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D59" s="17" t="str">
+        <x:v>#AD80FF</x:v>
+      </x:c>
+      <x:c r="E59" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F59" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G59" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" s="17" t="str">
+        <x:v>Damage_BossBlackHole</x:v>
+      </x:c>
+      <x:c r="B60" s="17" t="str">
+        <x:v>黑洞 -{damage}</x:v>
+      </x:c>
+      <x:c r="C60" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D60" s="17" t="str">
+        <x:v>#AD80FF</x:v>
+      </x:c>
+      <x:c r="E60" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F60" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G60" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" s="17" t="str">
+        <x:v>Damage_BossSolarFlare</x:v>
+      </x:c>
+      <x:c r="B61" s="17" t="str">
+        <x:v>日冕 -{damage}</x:v>
+      </x:c>
+      <x:c r="C61" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D61" s="17" t="str">
+        <x:v>#FFAA36</x:v>
+      </x:c>
+      <x:c r="E61" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F61" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G61" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" s="17" t="str">
+        <x:v>Damage_BossSunBrand</x:v>
+      </x:c>
+      <x:c r="B62" s="17" t="str">
+        <x:v>灼烧 -{damage}</x:v>
+      </x:c>
+      <x:c r="C62" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D62" s="17" t="str">
+        <x:v>#FFAA36</x:v>
+      </x:c>
+      <x:c r="E62" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F62" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G62" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" s="17" t="str">
+        <x:v>Damage_BossTidalSurge</x:v>
+      </x:c>
+      <x:c r="B63" s="17" t="str">
+        <x:v>怒涛 -{damage}</x:v>
+      </x:c>
+      <x:c r="C63" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D63" s="17" t="str">
+        <x:v>#40CCFF</x:v>
+      </x:c>
+      <x:c r="E63" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F63" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G63" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" s="17" t="str">
+        <x:v>Damage_BossMaelstrom</x:v>
+      </x:c>
+      <x:c r="B64" s="17" t="str">
+        <x:v>回流 -{damage}</x:v>
+      </x:c>
+      <x:c r="C64" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D64" s="17" t="str">
+        <x:v>#40CCFF</x:v>
+      </x:c>
+      <x:c r="E64" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F64" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G64" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" s="17" t="str">
+        <x:v>Damage_BossSwampMaw</x:v>
+      </x:c>
+      <x:c r="B65" s="17" t="str">
+        <x:v>吞噬 -{damage}</x:v>
+      </x:c>
+      <x:c r="C65" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D65" s="17" t="str">
+        <x:v>#8ECF48</x:v>
+      </x:c>
+      <x:c r="E65" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F65" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G65" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" s="17" t="str">
+        <x:v>Damage_BossMireChains</x:v>
+      </x:c>
+      <x:c r="B66" s="17" t="str">
+        <x:v>泥沼 -{damage}</x:v>
+      </x:c>
+      <x:c r="C66" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D66" s="17" t="str">
+        <x:v>#8ECF48</x:v>
+      </x:c>
+      <x:c r="E66" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F66" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G66" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" s="17" t="str">
+        <x:v>Damage_BossFrozenPrison</x:v>
+      </x:c>
+      <x:c r="B67" s="17" t="str">
+        <x:v>冰囚 -{damage}</x:v>
+      </x:c>
+      <x:c r="C67" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D67" s="17" t="str">
+        <x:v>#70E0FF</x:v>
+      </x:c>
+      <x:c r="E67" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F67" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G67" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" s="17" t="str">
+        <x:v>Damage_BossGlacialAegis</x:v>
+      </x:c>
+      <x:c r="B68" s="17" t="str">
+        <x:v>冰爆 -{damage}</x:v>
+      </x:c>
+      <x:c r="C68" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D68" s="17" t="str">
+        <x:v>#70E0FF</x:v>
+      </x:c>
+      <x:c r="E68" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F68" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G68" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" s="17" t="str">
+        <x:v>Damage_BossDivineCross</x:v>
+      </x:c>
+      <x:c r="B69" s="17" t="str">
+        <x:v>神罚 -{damage}</x:v>
+      </x:c>
+      <x:c r="C69" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D69" s="17" t="str">
+        <x:v>#FFDA50</x:v>
+      </x:c>
+      <x:c r="E69" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F69" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G69" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" s="17" t="str">
+        <x:v>Damage_BossSanctuary</x:v>
+      </x:c>
+      <x:c r="B70" s="17" t="str">
+        <x:v>圣域 -{damage}</x:v>
+      </x:c>
+      <x:c r="C70" s="17" t="str">
+        <x:v>真实扣血；仅同目标同来源合并</x:v>
+      </x:c>
+      <x:c r="D70" s="17" t="str">
+        <x:v>#FFDA50</x:v>
+      </x:c>
+      <x:c r="E70" s="17" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F70" s="17" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G70" s="17" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/RevGame_Client/配置表/战斗弹幕配置.xlsx
+++ b/RevGame_Client/配置表/战斗弹幕配置.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleText" sheetId="1" r:id="R4cb15cb319b049e9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleTuning" sheetId="2" r:id="R1872830242e24b63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="3" r:id="R18be5be65f724ad3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleText" sheetId="1" r:id="R1f107e3bcc1848ba"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BattleTuning" sheetId="2" r:id="R00bb8854a55344ec"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="#配置说明" sheetId="3" r:id="R8243ff5bcdca406a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1982,6 +1982,719 @@
         <x:v>1.32</x:v>
       </x:c>
     </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>Damage_BossCometRails</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>彗星轨道 -{damage}</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D71" t="str">
+        <x:v>#BD8AFF</x:v>
+      </x:c>
+      <x:c r="E71" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F71" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G71" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>Damage_BossAstralShards</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>星屑追爆 -{damage}</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D72" t="str">
+        <x:v>#BD8AFF</x:v>
+      </x:c>
+      <x:c r="E72" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F72" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G72" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>Damage_BossSolarSpears</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>烈阳贯枪 -{damage}</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D73" t="str">
+        <x:v>#FF993F</x:v>
+      </x:c>
+      <x:c r="E73" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F73" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G73" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>Damage_BossEmberFan</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>炎羽扇扫 -{damage}</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D74" t="str">
+        <x:v>#FF993F</x:v>
+      </x:c>
+      <x:c r="E74" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F74" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G74" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>Damage_BossMagmaRings</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>熔岩环爆 -{damage}</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D75" t="str">
+        <x:v>#FF993F</x:v>
+      </x:c>
+      <x:c r="E75" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F75" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G75" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>Damage_BossTidalLances</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>潮汐水枪 -{damage}</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D76" t="str">
+        <x:v>#61DDFF</x:v>
+      </x:c>
+      <x:c r="E76" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F76" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G76" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>Damage_BossFoamBurst</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>泡沫连爆 -{damage}</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D77" t="str">
+        <x:v>#61DDFF</x:v>
+      </x:c>
+      <x:c r="E77" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F77" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G77" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>Damage_BossUndertow</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>暗流绞阵 -{damage}</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D78" t="str">
+        <x:v>#61DDFF</x:v>
+      </x:c>
+      <x:c r="E78" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F78" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G78" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>Damage_BossReefSpikes</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>礁岩穿刺 -{damage}</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D79" t="str">
+        <x:v>#61DDFF</x:v>
+      </x:c>
+      <x:c r="E79" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F79" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G79" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>Damage_BossBogSpines</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>腐沼骨刺 -{damage}</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D80" t="str">
+        <x:v>#A8E65C</x:v>
+      </x:c>
+      <x:c r="E80" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F80" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G80" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>Damage_BossVenomFan</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>毒雾扇潮 -{damage}</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D81" t="str">
+        <x:v>#A8E65C</x:v>
+      </x:c>
+      <x:c r="E81" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F81" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G81" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>Damage_BossMireRipples</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>泥潭连震 -{damage}</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D82" t="str">
+        <x:v>#A8E65C</x:v>
+      </x:c>
+      <x:c r="E82" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F82" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G82" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str">
+        <x:v>Damage_BossBlightSeeds</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>疫种爆裂 -{damage}</x:v>
+      </x:c>
+      <x:c r="C83" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D83" t="str">
+        <x:v>#A8E65C</x:v>
+      </x:c>
+      <x:c r="E83" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F83" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G83" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>Damage_BossSnowCross</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>寒霜十字 -{damage}</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D84" t="str">
+        <x:v>#BAF1FF</x:v>
+      </x:c>
+      <x:c r="E84" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F84" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G84" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>Damage_BossHailBarrage</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>冰雹连坠 -{damage}</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D85" t="str">
+        <x:v>#BAF1FF</x:v>
+      </x:c>
+      <x:c r="E85" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F85" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G85" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>Damage_BossIceFault</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>冰川断层 -{damage}</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D86" t="str">
+        <x:v>#BAF1FF</x:v>
+      </x:c>
+      <x:c r="E86" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F86" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G86" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>Damage_BossJudgementLances</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>裁决光矛 -{damage}</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D87" t="str">
+        <x:v>#FFE48A</x:v>
+      </x:c>
+      <x:c r="E87" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F87" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G87" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>Damage_BossHaloPulse</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>圣环脉冲 -{damage}</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D88" t="str">
+        <x:v>#FFE48A</x:v>
+      </x:c>
+      <x:c r="E88" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F88" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G88" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>Damage_BossRunicGrid</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>律令棋阵 -{damage}</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D89" t="str">
+        <x:v>#FFE48A</x:v>
+      </x:c>
+      <x:c r="E89" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F89" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G89" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>Damage_BossEventHorizon</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>星界崩塌 -{damage}</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D90" t="str">
+        <x:v>#BD8AFF</x:v>
+      </x:c>
+      <x:c r="E90" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F90" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G90" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>Damage_BossConstellationSeal</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>星座封阵 -{damage}</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D91" t="str">
+        <x:v>#BD8AFF</x:v>
+      </x:c>
+      <x:c r="E91" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F91" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G91" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>Damage_BossPhoenixDescent</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>焚天凤陨 -{damage}</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D92" t="str">
+        <x:v>#FF993F</x:v>
+      </x:c>
+      <x:c r="E92" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F92" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G92" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>Damage_BossSolarEclipse</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>日蚀审判 -{damage}</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D93" t="str">
+        <x:v>#FF993F</x:v>
+      </x:c>
+      <x:c r="E93" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F93" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G93" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>Damage_BossLeviathanWake</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>巨鲸破浪 -{damage}</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D94" t="str">
+        <x:v>#61DDFF</x:v>
+      </x:c>
+      <x:c r="E94" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F94" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G94" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>Damage_BossAbyssalCage</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>深渊潮牢 -{damage}</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D95" t="str">
+        <x:v>#61DDFF</x:v>
+      </x:c>
+      <x:c r="E95" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F95" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G95" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>Damage_BossPlagueBloom</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>瘟疫绽放 -{damage}</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D96" t="str">
+        <x:v>#A8E65C</x:v>
+      </x:c>
+      <x:c r="E96" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F96" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G96" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>Damage_BossHydraFangs</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>九首獠牙 -{damage}</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D97" t="str">
+        <x:v>#A8E65C</x:v>
+      </x:c>
+      <x:c r="E97" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F97" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G97" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>Damage_BossAbsoluteZero</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>绝对零域 -{damage}</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D98" t="str">
+        <x:v>#BAF1FF</x:v>
+      </x:c>
+      <x:c r="E98" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F98" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G98" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>Damage_BossAvalanche</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>万仞雪崩 -{damage}</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D99" t="str">
+        <x:v>#BAF1FF</x:v>
+      </x:c>
+      <x:c r="E99" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F99" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G99" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>Damage_BossHeavenfall</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>天穹裁决 -{damage}</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D100" t="str">
+        <x:v>#FFE48A</x:v>
+      </x:c>
+      <x:c r="E100" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F100" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G100" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>Damage_BossFinalEdict</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>终极律令 -{damage}</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>真实扣血；同目标同来源合并。</x:v>
+      </x:c>
+      <x:c r="D101" t="str">
+        <x:v>#FFE48A</x:v>
+      </x:c>
+      <x:c r="E101" t="n">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="F101" t="n">
+        <x:v>1.1</x:v>
+      </x:c>
+      <x:c r="G101" t="n">
+        <x:v>1.32</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
